--- a/09_Risk_Management/_template_RISK.xlsx
+++ b/09_Risk_Management/_template_RISK.xlsx
@@ -12,7 +12,8 @@
     <sheet name="VaR" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Stress Scenarios" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="Sensitivity" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="RefreshLog" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Portfolio VaR (Multi-Asset)" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="RefreshLog" sheetId="6" state="visible" r:id="rId8"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="70">
   <si>
     <t xml:space="preserve">[PORTFOLIO] — Risk Management Model</t>
   </si>
@@ -150,6 +151,72 @@
   </si>
   <si>
     <t xml:space="preserve">Daily vol \ Confidence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portfolio VaR — Multi-Asset with Correlation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidence level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Z-score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Positions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$ Exposure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daily Vol %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standalone 1-day VaR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Position A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Position B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Position C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Correlation matrix (fill upper triangle; mirrored below)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portfolio Aggregation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portfolio variance ($^2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portfolio standard deviation ($)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portfolio 1-day VaR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Undiversified VaR (sum of standalone position VaRs)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diversification benefit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Always &gt;= 0 unless correlations are all exactly 1 -- this is the entire point of not underwriting each position in isolation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Component VaR (marginal contribution to portfolio risk)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sum of component VaRs (check — must equal Portfolio 1-day VaR exactly)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Euler's homogeneity theorem: for a variance-based risk measure, marginal contributions always sum exactly to the total -- a built-in formula check, not a coincidence</t>
   </si>
   <si>
     <t xml:space="preserve">Refresh Log</t>
@@ -174,15 +241,17 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="8">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
     <numFmt numFmtId="166" formatCode="0.00%;\(0.00%\);\-"/>
     <numFmt numFmtId="167" formatCode="0.0%;\(0.0%\);\-"/>
     <numFmt numFmtId="168" formatCode="#,##0;\(#,##0\);\-"/>
     <numFmt numFmtId="169" formatCode="0.0000"/>
+    <numFmt numFmtId="170" formatCode="0.00"/>
+    <numFmt numFmtId="171" formatCode="#,##0"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -249,6 +318,13 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF008000"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -325,7 +401,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="28">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -411,6 +487,26 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1485,6 +1581,275 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="B2:E30"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="40"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4" s="9" t="n">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5" s="11" t="n">
+        <f aca="false">NORMSINV(C4)</f>
+        <v>1.64485362695147</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="E8" s="18" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="8" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E9" s="12" t="n">
+        <f aca="false">IFERROR(C9*D9*$C$5,"-")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E10" s="12" t="n">
+        <f aca="false">IFERROR(C10*D10*$C$5,"-")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E11" s="12" t="n">
+        <f aca="false">IFERROR(C11*D11*$C$5,"-")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C14" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C15" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="23" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E15" s="23" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C16" s="24" t="n">
+        <f aca="false">D15</f>
+        <v>0.3</v>
+      </c>
+      <c r="D16" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="23" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C17" s="24" t="n">
+        <f aca="false">E15</f>
+        <v>0.3</v>
+      </c>
+      <c r="D17" s="24" t="n">
+        <f aca="false">E16</f>
+        <v>0.3</v>
+      </c>
+      <c r="E17" s="22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C20" s="25" t="n">
+        <f aca="false">C9*D9*C9*D9*C15+C9*D9*C10*D10*D15+C9*D9*C11*D11*E15+C10*D10*C9*D9*C16+C10*D10*C10*D10*D16+C10*D10*C11*D11*E16+C11*D11*C9*D9*C17+C11*D11*C10*D10*D17+C11*D11*C11*D11*E17</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C21" s="12" t="n">
+        <f aca="false">SQRT(C20)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C22" s="26" t="n">
+        <f aca="false">C21*C5</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C23" s="12" t="n">
+        <f aca="false">SUM(E9:E11)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C24" s="13" t="n">
+        <f aca="false">C23-C22</f>
+        <v>0</v>
+      </c>
+      <c r="D24" s="14" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C27" s="12" t="str">
+        <f aca="false">IFERROR((C9*(D9*(C9*D9*C15+C10*D10*D15+C11*D11*E15))/C20)*C22,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B28" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C28" s="12" t="str">
+        <f aca="false">IFERROR((C10*(D10*(C9*D9*C16+C10*D10*D16+C11*D11*E16))/C20)*C22,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B29" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C29" s="12" t="str">
+        <f aca="false">IFERROR((C11*(D11*(C9*D9*C17+C10*D10*D17+C11*D11*E17))/C20)*C22,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B30" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C30" s="13" t="n">
+        <f aca="false">SUM(C27:C29)</f>
+        <v>0</v>
+      </c>
+      <c r="D30" s="14" t="s">
+        <v>63</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="B2:F14"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -1497,95 +1862,95 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="17" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="22"/>
-      <c r="C5" s="22"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="22"/>
-      <c r="F5" s="22"/>
+      <c r="B5" s="27"/>
+      <c r="C5" s="27"/>
+      <c r="D5" s="27"/>
+      <c r="E5" s="27"/>
+      <c r="F5" s="27"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="22"/>
-      <c r="C6" s="22"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="22"/>
-      <c r="F6" s="22"/>
+      <c r="B6" s="27"/>
+      <c r="C6" s="27"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="27"/>
+      <c r="F6" s="27"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="22"/>
-      <c r="C7" s="22"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="22"/>
-      <c r="F7" s="22"/>
+      <c r="B7" s="27"/>
+      <c r="C7" s="27"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="27"/>
+      <c r="F7" s="27"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="22"/>
-      <c r="C8" s="22"/>
-      <c r="D8" s="22"/>
-      <c r="E8" s="22"/>
-      <c r="F8" s="22"/>
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="27"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="22"/>
-      <c r="C9" s="22"/>
-      <c r="D9" s="22"/>
-      <c r="E9" s="22"/>
-      <c r="F9" s="22"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="27"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="22"/>
-      <c r="C10" s="22"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="22"/>
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="22"/>
-      <c r="C11" s="22"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="22"/>
-      <c r="F11" s="22"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="27"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="22"/>
-      <c r="C12" s="22"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="22"/>
-      <c r="F12" s="22"/>
+      <c r="B12" s="27"/>
+      <c r="C12" s="27"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="27"/>
+      <c r="F12" s="27"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="22"/>
-      <c r="C13" s="22"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="22"/>
-      <c r="F13" s="22"/>
+      <c r="B13" s="27"/>
+      <c r="C13" s="27"/>
+      <c r="D13" s="27"/>
+      <c r="E13" s="27"/>
+      <c r="F13" s="27"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="22"/>
-      <c r="C14" s="22"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="22"/>
-      <c r="F14" s="22"/>
+      <c r="B14" s="27"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="27"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="27"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/09_Risk_Management/_template_RISK.xlsx
+++ b/09_Risk_Management/_template_RISK.xlsx
@@ -13,7 +13,9 @@
     <sheet name="Stress Scenarios" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="Sensitivity" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="Portfolio VaR (Multi-Asset)" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="RefreshLog" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Sources" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Checks" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="RefreshLog" sheetId="8" state="visible" r:id="rId10"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -25,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="107">
   <si>
     <t xml:space="preserve">[PORTFOLIO] — Risk Management Model</t>
   </si>
@@ -114,6 +116,21 @@
     <t xml:space="preserve">Daily P&amp;L ($)</t>
   </si>
   <si>
+    <t xml:space="preserve">Parametric vs. Historical: Method Comparison</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parametric 1-day VaR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Historical 1-day VaR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ratio (Historical / Parametric)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parametric VaR assumes normally-distributed returns; if the actual P&amp;L history has fat tails or negative skew (crashes bigger/more frequent than a normal distribution predicts), historical VaR comes in higher and this ratio exceeds 1x -- a real, checkable signal that the normality assumption is understating tail risk, not just a rounding difference between two methods that should agree.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Stress Scenarios</t>
   </si>
   <si>
@@ -217,6 +234,102 @@
   </si>
   <si>
     <t xml:space="preserve">Euler's homogeneity theorem: for a variance-based risk measure, marginal contributions always sum exactly to the total -- a built-in formula check, not a coincidence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sources</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What each material assumption or convention in this model comes from.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assumption / convention</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As of</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parametric (variance-covariance) VaR, Z x sigma x portfolio value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standard RiskMetrics-style parametric VaR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standard practice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assumes normally-distributed returns -- see the Method Comparison rows for a direct check of how much that assumption understates tail risk in the actual P&amp;L history</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Historical VaR via PERCENTILE of trailing daily P&amp;L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standard non-parametric VaR methodology, makes no distributional assumption</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Requires a real, sufficiently long P&amp;L history (100 obs minimum recommended) -- garbage in, garbage out more than the parametric method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analytic Expected Shortfall under normality, sigma x phi(Z)/(1-confidence)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standard closed-form ES formula under the normal-distribution assumption</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same normality caveat as parametric VaR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portfolio VaR variance decomposition + Euler component VaR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standard multi-asset correlation-weighted VaR aggregation (modern portfolio theory applied to risk)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3-position example; generalizes to N positions but the explicit-sum formula would need to scale accordingly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Live reconciliation identities -- independent of the model's own formulas, must tie.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Result</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passes when</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Component VaRs sum exactly to portfolio VaR (Euler's homogeneity theorem)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 (exact) -- not an approximation, a mathematical identity for a variance-based risk measure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diversification benefit is never negative (undiversified VaR &gt;= portfolio VaR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRUE -- correlations below 1 can only reduce risk, never increase it, versus the undiversified sum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expected Shortfall is never less than VaR at the same confidence level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRUE -- ES is the average loss GIVEN VaR is breached, so it can only be worse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Historical VaR is positive whenever the P&amp;L sample actually has losses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRUE</t>
   </si>
   <si>
     <t xml:space="preserve">Refresh Log</t>
@@ -241,15 +354,17 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
+  <numFmts count="10">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
     <numFmt numFmtId="166" formatCode="0.00%;\(0.00%\);\-"/>
     <numFmt numFmtId="167" formatCode="0.0%;\(0.0%\);\-"/>
     <numFmt numFmtId="168" formatCode="#,##0;\(#,##0\);\-"/>
     <numFmt numFmtId="169" formatCode="0.0000"/>
-    <numFmt numFmtId="170" formatCode="0.00"/>
-    <numFmt numFmtId="171" formatCode="#,##0"/>
+    <numFmt numFmtId="170" formatCode="0.00\x"/>
+    <numFmt numFmtId="171" formatCode="0.00"/>
+    <numFmt numFmtId="172" formatCode="#,##0"/>
+    <numFmt numFmtId="173" formatCode="General"/>
   </numFmts>
   <fonts count="11">
     <font>
@@ -311,16 +426,16 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
+      <color rgb="FF008000"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF008000"/>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -401,7 +516,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="33">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -470,7 +585,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -490,23 +613,35 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="171" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="173" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -978,15 +1113,42 @@
       <c r="E24" s="16"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="5" t="s">
+        <v>29</v>
+      </c>
       <c r="E25" s="16"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C26" s="17" t="n">
+        <f aca="false">C12</f>
+        <v>0</v>
+      </c>
       <c r="E26" s="16"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C27" s="17" t="str">
+        <f aca="false">C21</f>
+        <v>-</v>
+      </c>
       <c r="E27" s="16"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B28" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C28" s="18" t="str">
+        <f aca="false">IFERROR(C27/C26,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="D28" s="14" t="s">
+        <v>33</v>
+      </c>
       <c r="E28" s="16"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1298,29 +1460,29 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="17"/>
-      <c r="B4" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="C4" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="D4" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="E4" s="18" t="s">
-        <v>33</v>
+      <c r="A4" s="19"/>
+      <c r="B4" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="E4" s="20" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5" s="19" t="n">
+        <v>39</v>
+      </c>
+      <c r="C5" s="21" t="n">
         <v>-0.4</v>
       </c>
       <c r="D5" s="12" t="n">
@@ -1328,14 +1490,14 @@
         <v>-0</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="C6" s="19" t="n">
+        <v>41</v>
+      </c>
+      <c r="C6" s="21" t="n">
         <v>-0.1</v>
       </c>
       <c r="D6" s="12" t="n">
@@ -1343,14 +1505,14 @@
         <v>-0</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="C7" s="19" t="n">
+        <v>42</v>
+      </c>
+      <c r="C7" s="21" t="n">
         <v>-0.08</v>
       </c>
       <c r="D7" s="12" t="n">
@@ -1358,14 +1520,14 @@
         <v>-0</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="C8" s="19" t="n">
+        <v>43</v>
+      </c>
+      <c r="C8" s="21" t="n">
         <v>-0.15</v>
       </c>
       <c r="D8" s="12" t="n">
@@ -1373,14 +1535,14 @@
         <v>-0</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="C9" s="19" t="n">
+        <v>44</v>
+      </c>
+      <c r="C9" s="21" t="n">
         <v>-0.25</v>
       </c>
       <c r="D9" s="12" t="n">
@@ -1388,7 +1550,7 @@
         <v>-0</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -1417,31 +1579,31 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C4" s="20" t="n">
+        <v>46</v>
+      </c>
+      <c r="C4" s="22" t="n">
         <v>0.9</v>
       </c>
-      <c r="D4" s="20" t="n">
+      <c r="D4" s="22" t="n">
         <v>0.95</v>
       </c>
-      <c r="E4" s="20" t="n">
+      <c r="E4" s="22" t="n">
         <v>0.975</v>
       </c>
-      <c r="F4" s="20" t="n">
+      <c r="F4" s="22" t="n">
         <v>0.99</v>
       </c>
-      <c r="G4" s="20" t="n">
+      <c r="G4" s="22" t="n">
         <v>0.995</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="21" t="n">
+      <c r="B5" s="23" t="n">
         <v>0.01</v>
       </c>
       <c r="C5" s="12" t="n">
@@ -1466,7 +1628,7 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="21" t="n">
+      <c r="B6" s="23" t="n">
         <v>0.015</v>
       </c>
       <c r="C6" s="12" t="n">
@@ -1491,7 +1653,7 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="21" t="n">
+      <c r="B7" s="23" t="n">
         <v>0.02</v>
       </c>
       <c r="C7" s="12" t="n">
@@ -1516,7 +1678,7 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="21" t="n">
+      <c r="B8" s="23" t="n">
         <v>0.025</v>
       </c>
       <c r="C8" s="12" t="n">
@@ -1541,7 +1703,7 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="21" t="n">
+      <c r="B9" s="23" t="n">
         <v>0.03</v>
       </c>
       <c r="C9" s="12" t="n">
@@ -1592,12 +1754,12 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="1" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C4" s="9" t="n">
         <v>0.95</v>
@@ -1605,7 +1767,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="1" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C5" s="11" t="n">
         <f aca="false">NORMSINV(C4)</f>
@@ -1614,26 +1776,26 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="5" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="C8" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="D8" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="E8" s="18" t="s">
-        <v>49</v>
+      <c r="B8" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="E8" s="20" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="6" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>0</v>
@@ -1648,7 +1810,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C10" s="7" t="n">
         <v>0</v>
@@ -1663,7 +1825,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="6" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C11" s="7" t="n">
         <v>0</v>
@@ -1678,82 +1840,82 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="5" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C14" s="5" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C15" s="22" t="n">
+        <v>55</v>
+      </c>
+      <c r="C15" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="D15" s="23" t="n">
+      <c r="D15" s="25" t="n">
         <v>0.3</v>
       </c>
-      <c r="E15" s="23" t="n">
+      <c r="E15" s="25" t="n">
         <v>0.3</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C16" s="24" t="n">
+        <v>56</v>
+      </c>
+      <c r="C16" s="26" t="n">
         <f aca="false">D15</f>
         <v>0.3</v>
       </c>
-      <c r="D16" s="22" t="n">
+      <c r="D16" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="E16" s="23" t="n">
+      <c r="E16" s="25" t="n">
         <v>0.3</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C17" s="24" t="n">
+        <v>57</v>
+      </c>
+      <c r="C17" s="26" t="n">
         <f aca="false">E15</f>
         <v>0.3</v>
       </c>
-      <c r="D17" s="24" t="n">
+      <c r="D17" s="26" t="n">
         <f aca="false">E16</f>
         <v>0.3</v>
       </c>
-      <c r="E17" s="22" t="n">
+      <c r="E17" s="24" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="5" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C20" s="25" t="n">
+        <v>60</v>
+      </c>
+      <c r="C20" s="27" t="n">
         <f aca="false">C9*D9*C9*D9*C15+C9*D9*C10*D10*D15+C9*D9*C11*D11*E15+C10*D10*C9*D9*C16+C10*D10*C10*D10*D16+C10*D10*C11*D11*E16+C11*D11*C9*D9*C17+C11*D11*C10*D10*D17+C11*D11*C11*D11*E17</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="1" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C21" s="12" t="n">
         <f aca="false">SQRT(C20)</f>
@@ -1762,16 +1924,16 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C22" s="26" t="n">
+        <v>62</v>
+      </c>
+      <c r="C22" s="28" t="n">
         <f aca="false">C21*C5</f>
         <v>0</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="1" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C23" s="12" t="n">
         <f aca="false">SUM(E9:E11)</f>
@@ -1780,24 +1942,24 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="1" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C24" s="13" t="n">
         <f aca="false">C23-C22</f>
         <v>0</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="5" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="6" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="C27" s="12" t="str">
         <f aca="false">IFERROR((C9*(D9*(C9*D9*C15+C10*D10*D15+C11*D11*E15))/C20)*C22,"-")</f>
@@ -1806,7 +1968,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C28" s="12" t="str">
         <f aca="false">IFERROR((C10*(D10*(C9*D9*C16+C10*D10*D16+C11*D11*E16))/C20)*C22,"-")</f>
@@ -1815,7 +1977,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="6" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C29" s="12" t="str">
         <f aca="false">IFERROR((C11*(D11*(C9*D9*C17+C10*D10*D17+C11*D11*E17))/C20)*C22,"-")</f>
@@ -1824,14 +1986,14 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C30" s="13" t="n">
         <f aca="false">SUM(C27:C29)</f>
         <v>0</v>
       </c>
       <c r="D30" s="14" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -1850,6 +2012,206 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="B2:E9"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="46"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B3" s="14" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="29" t="s">
+        <v>75</v>
+      </c>
+      <c r="C6" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="D6" s="29" t="s">
+        <v>77</v>
+      </c>
+      <c r="E6" s="30" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="C7" s="29" t="s">
+        <v>80</v>
+      </c>
+      <c r="D7" s="29" t="s">
+        <v>77</v>
+      </c>
+      <c r="E7" s="30" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="29" t="s">
+        <v>82</v>
+      </c>
+      <c r="C8" s="29" t="s">
+        <v>83</v>
+      </c>
+      <c r="D8" s="29" t="s">
+        <v>77</v>
+      </c>
+      <c r="E8" s="30" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="29" t="s">
+        <v>85</v>
+      </c>
+      <c r="C9" s="29" t="s">
+        <v>86</v>
+      </c>
+      <c r="D9" s="29" t="s">
+        <v>77</v>
+      </c>
+      <c r="E9" s="30" t="s">
+        <v>87</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="B2:D9"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="46"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B3" s="14" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="29" t="s">
+        <v>93</v>
+      </c>
+      <c r="C6" s="31" t="n">
+        <f aca="false">'Portfolio VaR (Multi-Asset)'!C30-'Portfolio VaR (Multi-Asset)'!C22</f>
+        <v>0</v>
+      </c>
+      <c r="D6" s="30" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="29" t="s">
+        <v>95</v>
+      </c>
+      <c r="C7" s="31" t="b">
+        <f aca="false">IF('Portfolio VaR (Multi-Asset)'!C24&gt;=-0.01,TRUE(),FALSE())</f>
+        <v>1</v>
+      </c>
+      <c r="D7" s="30" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="29" t="s">
+        <v>97</v>
+      </c>
+      <c r="C8" s="31" t="b">
+        <f aca="false">IF(OR(NOT(ISNUMBER(VaR!C15)),NOT(ISNUMBER(VaR!C12))),TRUE(),VaR!C15&gt;=VaR!C12-0.01)</f>
+        <v>1</v>
+      </c>
+      <c r="D8" s="30" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="29" t="s">
+        <v>99</v>
+      </c>
+      <c r="C9" s="31" t="b">
+        <f aca="false">IF(COUNTIF(VaR!E23:E122,"&lt;0")=0,TRUE(),VaR!C21&gt;0)</f>
+        <v>1</v>
+      </c>
+      <c r="D9" s="30" t="s">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="B2:F14"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -1862,95 +2224,95 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>64</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="17" t="s">
-        <v>65</v>
-      </c>
-      <c r="C4" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="D4" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="E4" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="F4" s="17" t="s">
-        <v>69</v>
+      <c r="B4" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="E4" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="F4" s="19" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="27"/>
-      <c r="C5" s="27"/>
-      <c r="D5" s="27"/>
-      <c r="E5" s="27"/>
-      <c r="F5" s="27"/>
+      <c r="B5" s="32"/>
+      <c r="C5" s="32"/>
+      <c r="D5" s="32"/>
+      <c r="E5" s="32"/>
+      <c r="F5" s="32"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="27"/>
-      <c r="C6" s="27"/>
-      <c r="D6" s="27"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="27"/>
+      <c r="B6" s="32"/>
+      <c r="C6" s="32"/>
+      <c r="D6" s="32"/>
+      <c r="E6" s="32"/>
+      <c r="F6" s="32"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="27"/>
-      <c r="C7" s="27"/>
-      <c r="D7" s="27"/>
-      <c r="E7" s="27"/>
-      <c r="F7" s="27"/>
+      <c r="B7" s="32"/>
+      <c r="C7" s="32"/>
+      <c r="D7" s="32"/>
+      <c r="E7" s="32"/>
+      <c r="F7" s="32"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="27"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="27"/>
+      <c r="B8" s="32"/>
+      <c r="C8" s="32"/>
+      <c r="D8" s="32"/>
+      <c r="E8" s="32"/>
+      <c r="F8" s="32"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="27"/>
-      <c r="C9" s="27"/>
-      <c r="D9" s="27"/>
-      <c r="E9" s="27"/>
-      <c r="F9" s="27"/>
+      <c r="B9" s="32"/>
+      <c r="C9" s="32"/>
+      <c r="D9" s="32"/>
+      <c r="E9" s="32"/>
+      <c r="F9" s="32"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="27"/>
-      <c r="C10" s="27"/>
-      <c r="D10" s="27"/>
-      <c r="E10" s="27"/>
-      <c r="F10" s="27"/>
+      <c r="B10" s="32"/>
+      <c r="C10" s="32"/>
+      <c r="D10" s="32"/>
+      <c r="E10" s="32"/>
+      <c r="F10" s="32"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="27"/>
-      <c r="C11" s="27"/>
-      <c r="D11" s="27"/>
-      <c r="E11" s="27"/>
-      <c r="F11" s="27"/>
+      <c r="B11" s="32"/>
+      <c r="C11" s="32"/>
+      <c r="D11" s="32"/>
+      <c r="E11" s="32"/>
+      <c r="F11" s="32"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="27"/>
-      <c r="C12" s="27"/>
-      <c r="D12" s="27"/>
-      <c r="E12" s="27"/>
-      <c r="F12" s="27"/>
+      <c r="B12" s="32"/>
+      <c r="C12" s="32"/>
+      <c r="D12" s="32"/>
+      <c r="E12" s="32"/>
+      <c r="F12" s="32"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="27"/>
-      <c r="C13" s="27"/>
-      <c r="D13" s="27"/>
-      <c r="E13" s="27"/>
-      <c r="F13" s="27"/>
+      <c r="B13" s="32"/>
+      <c r="C13" s="32"/>
+      <c r="D13" s="32"/>
+      <c r="E13" s="32"/>
+      <c r="F13" s="32"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="27"/>
-      <c r="C14" s="27"/>
-      <c r="D14" s="27"/>
-      <c r="E14" s="27"/>
-      <c r="F14" s="27"/>
+      <c r="B14" s="32"/>
+      <c r="C14" s="32"/>
+      <c r="D14" s="32"/>
+      <c r="E14" s="32"/>
+      <c r="F14" s="32"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
